--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9051,0.0286,0.0090,0.0258</t>
-  </si>
-  <si>
-    <t>0.0211,0.0008,0.0005,0.9930</t>
-  </si>
-  <si>
-    <t>0.8355,0.0043,0.0022,0.1678</t>
-  </si>
-  <si>
-    <t>0.0155,0.0046,0.0033,0.9908</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9978,0.0003,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9969,0.0016,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9917,0.0059,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9958,0.0048,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9964,0.0012,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9973,0.0009,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.7671,0.0391,0.2386,0.0013</t>
-  </si>
-  <si>
-    <t>0.1056,0.0272,0.9150,0.0001</t>
-  </si>
-  <si>
-    <t>0.0541,0.0633,0.9414,0.0001</t>
-  </si>
-  <si>
-    <t>0.7661,0.0040,0.2925,0.0094</t>
-  </si>
-  <si>
-    <t>0.8077,0.0908,0.0702,0.0206</t>
-  </si>
-  <si>
-    <t>0.0166,0.9794,0.0037,0.0002</t>
-  </si>
-  <si>
-    <t>0.0654,0.9635,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.0853,0.9394,0.0050,0.0006</t>
-  </si>
-  <si>
-    <t>0.0145,0.9828,0.0033,0.0001</t>
-  </si>
-  <si>
-    <t>0.0103,0.9886,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.6933,0.0039,0.4856,0.0024</t>
-  </si>
-  <si>
-    <t>0.4263,0.0061,0.7259,0.0023</t>
-  </si>
-  <si>
-    <t>0.0676,0.0193,0.9388,0.0037</t>
-  </si>
-  <si>
-    <t>0.1749,0.0200,0.8299,0.0196</t>
-  </si>
-  <si>
-    <t>0.0791,0.0033,0.9581,0.0007</t>
-  </si>
-  <si>
-    <t>0.1479,0.0030,0.8892,0.0062</t>
-  </si>
-  <si>
-    <t>0.0090,0.0049,0.9868,0.0014</t>
-  </si>
-  <si>
-    <t>0.5313,0.5306,0.0199,0.0040</t>
-  </si>
-  <si>
-    <t>0.2315,0.5317,0.2634,0.0018</t>
-  </si>
-  <si>
-    <t>0.0032,0.0029,0.9949,0.0012</t>
-  </si>
-  <si>
-    <t>0.0054,0.9553,0.1217,0.0010</t>
-  </si>
-  <si>
-    <t>0.8987,0.0435,0.0215,0.0217</t>
-  </si>
-  <si>
-    <t>0.9019,0.0399,0.0683,0.0054</t>
-  </si>
-  <si>
-    <t>0.8470,0.2963,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.0637,0.7687,0.5330,0.0162</t>
-  </si>
-  <si>
-    <t>0.0177,0.5236,0.1506,0.2831</t>
-  </si>
-  <si>
-    <t>0.0342,0.0194,0.9340,0.0267</t>
-  </si>
-  <si>
-    <t>0.2210,0.1464,0.6970,0.0691</t>
-  </si>
-  <si>
-    <t>0.0880,0.0041,0.9144,0.0174</t>
-  </si>
-  <si>
-    <t>0.0091,0.1482,0.9656,0.0038</t>
-  </si>
-  <si>
-    <t>0.0022,0.9804,0.0128,0.0002</t>
-  </si>
-  <si>
-    <t>0.0323,0.0214,0.9507,0.0087</t>
-  </si>
-  <si>
-    <t>0.0351,0.7645,0.0084,0.5310</t>
-  </si>
-  <si>
-    <t>0.0112,0.9710,0.0168,0.0025</t>
-  </si>
-  <si>
-    <t>0.0101,0.9682,0.0562,0.0010</t>
-  </si>
-  <si>
-    <t>0.0033,0.9892,0.0052,0.0020</t>
-  </si>
-  <si>
-    <t>0.0124,0.1189,0.9236,0.0311</t>
-  </si>
-  <si>
-    <t>0.0018,0.0219,0.9849,0.0072</t>
-  </si>
-  <si>
-    <t>0.0367,0.1014,0.8845,0.0363</t>
-  </si>
-  <si>
-    <t>0.0350,0.0016,0.9732,0.0022</t>
-  </si>
-  <si>
-    <t>0.0233,0.0161,0.9659,0.0038</t>
-  </si>
-  <si>
-    <t>0.0207,0.0671,0.9592,0.0016</t>
-  </si>
-  <si>
-    <t>0.9820,0.0285,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9810,0.0038,0.0073,0.0018</t>
-  </si>
-  <si>
-    <t>0.9633,0.0466,0.0010,0.0013</t>
-  </si>
-  <si>
-    <t>0.0040,0.2962,0.9730,0.0011</t>
-  </si>
-  <si>
-    <t>0.9935,0.0061,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9941,0.0021,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9526,0.0557,0.0040,0.0017</t>
-  </si>
-  <si>
-    <t>0.0089,0.7946,0.7811,0.0085</t>
-  </si>
-  <si>
-    <t>0.0092,0.0282,0.9673,0.0112</t>
-  </si>
-  <si>
-    <t>0.0260,0.0669,0.8603,0.0743</t>
-  </si>
-  <si>
-    <t>0.0020,0.8101,0.9661,0.0008</t>
-  </si>
-  <si>
-    <t>0.0048,0.0206,0.9780,0.0084</t>
-  </si>
-  <si>
-    <t>0.0941,0.7591,0.1339,0.0006</t>
-  </si>
-  <si>
-    <t>0.0063,0.9829,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9341,0.0239,0.0238,0.0038</t>
-  </si>
-  <si>
-    <t>0.8296,0.1257,0.0701,0.0077</t>
-  </si>
-  <si>
-    <t>0.0208,0.1258,0.8681,0.0010</t>
-  </si>
-  <si>
-    <t>0.0012,0.6787,0.9739,0.0002</t>
-  </si>
-  <si>
-    <t>0.0145,0.7743,0.7278,0.0018</t>
-  </si>
-  <si>
-    <t>0.0008,0.9774,0.4082,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.9673,0.3981,0.0010</t>
-  </si>
-  <si>
-    <t>0.0087,0.0005,0.0219,0.9842</t>
-  </si>
-  <si>
-    <t>0.0031,0.0092,0.0002,0.9976</t>
-  </si>
-  <si>
-    <t>0.0108,0.0045,0.0002,0.9958</t>
-  </si>
-  <si>
-    <t>0.1003,0.0055,0.0054,0.9510</t>
-  </si>
-  <si>
-    <t>0.0038,0.0039,0.0034,0.9962</t>
-  </si>
-  <si>
-    <t>0.0017,0.0009,0.0001,0.9992</t>
-  </si>
-  <si>
-    <t>0.0003,0.9790,0.7887,0.0000</t>
-  </si>
-  <si>
-    <t>0.0031,0.6936,0.9521,0.0006</t>
-  </si>
-  <si>
-    <t>0.0231,0.5489,0.5588,0.0019</t>
-  </si>
-  <si>
-    <t>0.0085,0.7637,0.7765,0.0011</t>
-  </si>
-  <si>
-    <t>0.0013,0.9187,0.8384,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.6888,0.9675,0.0002</t>
-  </si>
-  <si>
-    <t>0.9952,0.0033,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9882,0.0204,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9888,0.0142,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9899,0.0063,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9922,0.0052,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9973,0.0021,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9924,0.0113,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9962,0.0023,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9975,0.0004,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9969,0.0017,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9983,0.0006,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9971,0.0005,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.9976,0.0006,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0157,0.0020,0.9803,0.0054</t>
-  </si>
-  <si>
-    <t>0.1159,0.0082,0.9452,0.0006</t>
-  </si>
-  <si>
-    <t>0.6883,0.0295,0.2807,0.0398</t>
-  </si>
-  <si>
-    <t>0.0086,0.0019,0.9796,0.0176</t>
-  </si>
-  <si>
-    <t>0.0228,0.9770,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.0140,0.9781,0.0051,0.0004</t>
-  </si>
-  <si>
-    <t>0.0689,0.9487,0.0029,0.0003</t>
-  </si>
-  <si>
-    <t>0.3475,0.7336,0.0097,0.0022</t>
-  </si>
-  <si>
-    <t>0.0303,0.9721,0.0034,0.0003</t>
-  </si>
-  <si>
-    <t>0.0052,0.9909,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.6774,0.4638,0.0092,0.0016</t>
-  </si>
-  <si>
-    <t>0.6374,0.0840,0.3543,0.0262</t>
-  </si>
-  <si>
-    <t>0.7216,0.0284,0.3287,0.0105</t>
-  </si>
-  <si>
-    <t>0.4826,0.3611,0.1794,0.0349</t>
-  </si>
-  <si>
-    <t>0.7254,0.0302,0.3126,0.0011</t>
-  </si>
-  <si>
-    <t>0.1310,0.2488,0.1805,0.7735</t>
-  </si>
-  <si>
-    <t>0.0102,0.9833,0.0047,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.9964,0.0007,0.0014</t>
-  </si>
-  <si>
-    <t>0.0303,0.9320,0.0177,0.0187</t>
-  </si>
-  <si>
-    <t>0.0040,0.9182,0.7821,0.0037</t>
-  </si>
-  <si>
-    <t>0.0227,0.9700,0.0103,0.0010</t>
-  </si>
-  <si>
-    <t>0.6519,0.4973,0.0080,0.0002</t>
-  </si>
-  <si>
-    <t>0.5394,0.5604,0.0148,0.0003</t>
-  </si>
-  <si>
-    <t>0.9888,0.0036,0.0005,0.0028</t>
-  </si>
-  <si>
-    <t>0.9891,0.0022,0.0016,0.0019</t>
-  </si>
-  <si>
-    <t>0.9959,0.0006,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9970,0.0006,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9959,0.0012,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9750,0.0143,0.0057,0.0014</t>
-  </si>
-  <si>
-    <t>0.9935,0.0013,0.0005,0.0015</t>
-  </si>
-  <si>
-    <t>0.9966,0.0002,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.0010,0.8178,0.9622,0.0009</t>
-  </si>
-  <si>
-    <t>0.0309,0.2199,0.9123,0.0005</t>
-  </si>
-  <si>
-    <t>0.0120,0.2044,0.9476,0.0024</t>
-  </si>
-  <si>
-    <t>0.0183,0.2360,0.8875,0.0023</t>
-  </si>
-  <si>
-    <t>0.7969,0.0584,0.0338,0.0434</t>
-  </si>
-  <si>
-    <t>0.6816,0.1859,0.1294,0.0299</t>
-  </si>
-  <si>
-    <t>0.3231,0.0047,0.7397,0.0191</t>
-  </si>
-  <si>
-    <t>0.5555,0.1988,0.2942,0.0347</t>
-  </si>
-  <si>
-    <t>0.2687,0.0004,0.0004,0.8954</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0185,0.0019,0.0005,0.9944</t>
-  </si>
-  <si>
-    <t>0.0093,0.0006,0.0004,0.9967</t>
-  </si>
-  <si>
-    <t>0.0088,0.4529,0.8947,0.0090</t>
-  </si>
-  <si>
-    <t>0.9901,0.0074,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.1002,0.9021,0.0024,0.0035</t>
-  </si>
-  <si>
-    <t>0.9820,0.0107,0.0025,0.0010</t>
-  </si>
-  <si>
-    <t>0.5712,0.6010,0.0018,0.0014</t>
-  </si>
-  <si>
-    <t>0.9845,0.0038,0.0026,0.0022</t>
-  </si>
-  <si>
-    <t>0.7181,0.0036,0.0046,0.3141</t>
-  </si>
-  <si>
-    <t>0.9883,0.0008,0.0002,0.0060</t>
-  </si>
-  <si>
-    <t>0.0013,0.0192,0.9600,0.1000</t>
-  </si>
-  <si>
-    <t>0.9004,0.0009,0.0176,0.0413</t>
-  </si>
-  <si>
-    <t>0.9871,0.0023,0.0035,0.0012</t>
-  </si>
-  <si>
-    <t>0.5081,0.5479,0.0295,0.0039</t>
-  </si>
-  <si>
-    <t>0.9480,0.0353,0.0093,0.0016</t>
-  </si>
-  <si>
-    <t>0.8184,0.1568,0.0596,0.0031</t>
-  </si>
-  <si>
-    <t>0.5101,0.5766,0.0109,0.0065</t>
-  </si>
-  <si>
-    <t>0.7705,0.1520,0.0527,0.0385</t>
-  </si>
-  <si>
-    <t>0.8106,0.1129,0.0625,0.0123</t>
-  </si>
-  <si>
-    <t>0.9959,0.0008,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9914,0.0048,0.0003,0.0010</t>
-  </si>
-  <si>
-    <t>0.9968,0.0005,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9923,0.0006,0.0004,0.0027</t>
-  </si>
-  <si>
-    <t>0.9961,0.0005,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9951,0.0010,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.9900,0.0030,0.0004,0.0022</t>
-  </si>
-  <si>
-    <t>0.9961,0.0003,0.0000,0.0012</t>
-  </si>
-  <si>
-    <t>0.3387,0.6504,0.0110,0.0270</t>
-  </si>
-  <si>
-    <t>0.4641,0.6043,0.0231,0.0012</t>
-  </si>
-  <si>
-    <t>0.8140,0.3159,0.0044,0.0002</t>
-  </si>
-  <si>
-    <t>0.5767,0.4538,0.0602,0.0040</t>
-  </si>
-  <si>
-    <t>0.9119,0.1899,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.9462,0.0274,0.0264,0.0031</t>
-  </si>
-  <si>
-    <t>0.9867,0.0070,0.0016,0.0013</t>
-  </si>
-  <si>
-    <t>0.8240,0.2183,0.0012,0.0045</t>
-  </si>
-  <si>
-    <t>0.0104,0.0338,0.9895,0.0008</t>
-  </si>
-  <si>
-    <t>0.9681,0.0319,0.0064,0.0009</t>
-  </si>
-  <si>
-    <t>0.0191,0.0269,0.9782,0.0005</t>
-  </si>
-  <si>
-    <t>0.0027,0.2964,0.9745,0.0033</t>
-  </si>
-  <si>
-    <t>0.2250,0.0163,0.8586,0.0034</t>
-  </si>
-  <si>
-    <t>0.0103,0.0359,0.9738,0.0008</t>
-  </si>
-  <si>
-    <t>0.0106,0.0139,0.9744,0.0030</t>
-  </si>
-  <si>
-    <t>0.0242,0.0038,0.9780,0.0010</t>
-  </si>
-  <si>
-    <t>0.0053,0.0146,0.9880,0.0017</t>
-  </si>
-  <si>
-    <t>0.0328,0.0220,0.9488,0.0028</t>
-  </si>
-  <si>
-    <t>0.3841,0.0448,0.6779,0.0032</t>
-  </si>
-  <si>
-    <t>0.5595,0.0379,0.5813,0.0053</t>
-  </si>
-  <si>
-    <t>0.4625,0.2730,0.3261,0.0076</t>
-  </si>
-  <si>
-    <t>0.2147,0.2266,0.6475,0.0027</t>
-  </si>
-  <si>
-    <t>0.4368,0.2326,0.3573,0.0037</t>
-  </si>
-  <si>
-    <t>0.6712,0.1066,0.2415,0.0405</t>
-  </si>
-  <si>
-    <t>0.2604,0.1513,0.6942,0.0063</t>
-  </si>
-  <si>
-    <t>0.6189,0.5571,0.0037,0.0002</t>
-  </si>
-  <si>
-    <t>0.3368,0.8099,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.8797,0.2210,0.0047,0.0004</t>
-  </si>
-  <si>
-    <t>0.9338,0.1485,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.9827,0.0346,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.6913,0.1880,0.1152,0.0027</t>
-  </si>
-  <si>
-    <t>0.8261,0.0598,0.0845,0.0141</t>
-  </si>
-  <si>
-    <t>0.7345,0.0356,0.0612,0.1185</t>
-  </si>
-  <si>
-    <t>0.5475,0.0317,0.3580,0.1081</t>
-  </si>
-  <si>
-    <t>0.6011,0.3356,0.0374,0.0415</t>
-  </si>
-  <si>
-    <t>0.0122,0.0069,0.9827,0.0011</t>
-  </si>
-  <si>
-    <t>0.0536,0.3009,0.8577,0.0080</t>
-  </si>
-  <si>
-    <t>0.2461,0.0558,0.7628,0.0122</t>
-  </si>
-  <si>
-    <t>0.2250,0.1634,0.5642,0.0017</t>
-  </si>
-  <si>
-    <t>0.0110,0.8482,0.2497,0.0026</t>
-  </si>
-  <si>
-    <t>0.9929,0.0042,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9912,0.0044,0.0003,0.0012</t>
-  </si>
-  <si>
-    <t>0.9944,0.0024,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9947,0.0018,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9896,0.0045,0.0037,0.0004</t>
-  </si>
-  <si>
-    <t>0.9948,0.0026,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9855,0.0030,0.0004,0.0039</t>
-  </si>
-  <si>
-    <t>0.9955,0.0032,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.1598,0.0209,0.8737,0.0149</t>
-  </si>
-  <si>
-    <t>0.3169,0.5710,0.0963,0.0171</t>
-  </si>
-  <si>
-    <t>0.8531,0.0644,0.0905,0.0069</t>
-  </si>
-  <si>
-    <t>0.0156,0.0733,0.9528,0.0033</t>
-  </si>
-  <si>
-    <t>0.0131,0.0125,0.9682,0.0078</t>
-  </si>
-  <si>
-    <t>0.0257,0.2395,0.8111,0.0003</t>
-  </si>
-  <si>
-    <t>0.0034,0.0039,0.9905,0.0039</t>
-  </si>
-  <si>
-    <t>0.0456,0.0100,0.9423,0.0037</t>
-  </si>
-  <si>
-    <t>0.0035,0.0035,0.9926,0.0017</t>
-  </si>
-  <si>
-    <t>0.0798,0.0381,0.9155,0.0045</t>
-  </si>
-  <si>
-    <t>0.0549,0.0346,0.9500,0.0032</t>
-  </si>
-  <si>
-    <t>0.7774,0.0151,0.2465,0.0112</t>
-  </si>
-  <si>
-    <t>0.4922,0.0907,0.5263,0.0121</t>
-  </si>
-  <si>
-    <t>0.8859,0.0053,0.0431,0.0333</t>
-  </si>
-  <si>
-    <t>0.9933,0.0074,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9950,0.0043,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9977,0.0011,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9968,0.0026,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0008,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9861,0.0298,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9959,0.0034,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9953,0.0021,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.0740,0.0608,0.8722,0.0005</t>
-  </si>
-  <si>
-    <t>0.0012,0.0598,0.9909,0.0011</t>
-  </si>
-  <si>
-    <t>0.0072,0.0539,0.9618,0.0077</t>
-  </si>
-  <si>
-    <t>0.0576,0.1631,0.6576,0.0001</t>
-  </si>
-  <si>
-    <t>0.0115,0.0093,0.9766,0.0048</t>
-  </si>
-  <si>
-    <t>0.0692,0.0097,0.8243,0.1275</t>
-  </si>
-  <si>
-    <t>0.1702,0.0734,0.8022,0.0108</t>
-  </si>
-  <si>
-    <t>0.0652,0.0856,0.7801,0.1852</t>
-  </si>
-  <si>
-    <t>0.3772,0.0049,0.0171,0.6862</t>
-  </si>
-  <si>
-    <t>0.0556,0.0832,0.0028,0.9620</t>
-  </si>
-  <si>
-    <t>0.0159,0.0014,0.0003,0.9954</t>
-  </si>
-  <si>
-    <t>0.0029,0.0006,0.0003,0.9986</t>
-  </si>
-  <si>
-    <t>0.0012,0.0005,0.0007,0.9990</t>
-  </si>
-  <si>
-    <t>0.8476,0.0270,0.0553,0.0370</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.8320,0.0548,0.0083,0.0573</t>
+  </si>
+  <si>
+    <t>0.0071,0.0019,0.0013,0.9960</t>
+  </si>
+  <si>
+    <t>0.7605,0.0230,0.0040,0.2182</t>
+  </si>
+  <si>
+    <t>0.0577,0.0008,0.0004,0.9845</t>
+  </si>
+  <si>
+    <t>0.9983,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9958,0.0025,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9973,0.0013,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9968,0.0017,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9964,0.0042,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9950,0.0053,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9972,0.0003,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.9970,0.0010,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.7375,0.0770,0.1640,0.0256</t>
+  </si>
+  <si>
+    <t>0.5395,0.1024,0.4350,0.0076</t>
+  </si>
+  <si>
+    <t>0.4701,0.0301,0.6781,0.0006</t>
+  </si>
+  <si>
+    <t>0.1692,0.0313,0.8246,0.0241</t>
+  </si>
+  <si>
+    <t>0.8162,0.0428,0.1638,0.0079</t>
+  </si>
+  <si>
+    <t>0.0047,0.9904,0.0051,0.0006</t>
+  </si>
+  <si>
+    <t>0.0529,0.9511,0.0024,0.0024</t>
+  </si>
+  <si>
+    <t>0.3212,0.8113,0.0034,0.0006</t>
+  </si>
+  <si>
+    <t>0.2535,0.8615,0.0032,0.0004</t>
+  </si>
+  <si>
+    <t>0.0059,0.9927,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.2823,0.0098,0.5596,0.1524</t>
+  </si>
+  <si>
+    <t>0.0910,0.0058,0.9143,0.0073</t>
+  </si>
+  <si>
+    <t>0.0124,0.0035,0.9782,0.0088</t>
+  </si>
+  <si>
+    <t>0.3805,0.0097,0.7002,0.0163</t>
+  </si>
+  <si>
+    <t>0.2199,0.0017,0.9053,0.0019</t>
+  </si>
+  <si>
+    <t>0.0998,0.0095,0.9222,0.0014</t>
+  </si>
+  <si>
+    <t>0.0025,0.0013,0.9709,0.1420</t>
+  </si>
+  <si>
+    <t>0.7074,0.4009,0.0094,0.0033</t>
+  </si>
+  <si>
+    <t>0.2447,0.2116,0.5746,0.0224</t>
+  </si>
+  <si>
+    <t>0.0009,0.0037,0.9922,0.0092</t>
+  </si>
+  <si>
+    <t>0.0025,0.9795,0.0337,0.0008</t>
+  </si>
+  <si>
+    <t>0.7482,0.3020,0.0278,0.0099</t>
+  </si>
+  <si>
+    <t>0.8004,0.1188,0.0854,0.0099</t>
+  </si>
+  <si>
+    <t>0.3175,0.8081,0.0052,0.0005</t>
+  </si>
+  <si>
+    <t>0.1093,0.8082,0.2803,0.0293</t>
+  </si>
+  <si>
+    <t>0.0078,0.8854,0.0187,0.0917</t>
+  </si>
+  <si>
+    <t>0.0949,0.1394,0.7921,0.0136</t>
+  </si>
+  <si>
+    <t>0.0309,0.1011,0.8199,0.1214</t>
+  </si>
+  <si>
+    <t>0.1713,0.0025,0.8598,0.0120</t>
+  </si>
+  <si>
+    <t>0.1248,0.2023,0.7452,0.0122</t>
+  </si>
+  <si>
+    <t>0.0035,0.9749,0.0065,0.0029</t>
+  </si>
+  <si>
+    <t>0.0076,0.0189,0.9646,0.0149</t>
+  </si>
+  <si>
+    <t>0.0453,0.7751,0.0114,0.4697</t>
+  </si>
+  <si>
+    <t>0.0416,0.9179,0.0121,0.0258</t>
+  </si>
+  <si>
+    <t>0.0094,0.9310,0.2958,0.0061</t>
+  </si>
+  <si>
+    <t>0.0071,0.9805,0.0122,0.0017</t>
+  </si>
+  <si>
+    <t>0.0130,0.2575,0.9058,0.0161</t>
+  </si>
+  <si>
+    <t>0.0021,0.0324,0.9896,0.0011</t>
+  </si>
+  <si>
+    <t>0.0501,0.0068,0.9452,0.0067</t>
+  </si>
+  <si>
+    <t>0.0129,0.0024,0.9864,0.0017</t>
+  </si>
+  <si>
+    <t>0.0055,0.0630,0.9645,0.0077</t>
+  </si>
+  <si>
+    <t>0.0045,0.0307,0.9808,0.0034</t>
+  </si>
+  <si>
+    <t>0.9436,0.1066,0.0035,0.0002</t>
+  </si>
+  <si>
+    <t>0.9921,0.0033,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.9849,0.0088,0.0039,0.0007</t>
+  </si>
+  <si>
+    <t>0.0042,0.0387,0.9860,0.0039</t>
+  </si>
+  <si>
+    <t>0.9915,0.0030,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9901,0.0122,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9904,0.0119,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0037,0.6776,0.9434,0.0036</t>
+  </si>
+  <si>
+    <t>0.0045,0.1078,0.9655,0.0085</t>
+  </si>
+  <si>
+    <t>0.0151,0.0168,0.9568,0.0341</t>
+  </si>
+  <si>
+    <t>0.0007,0.9585,0.9267,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.0028,0.9926,0.0086</t>
+  </si>
+  <si>
+    <t>0.0620,0.9121,0.0187,0.0013</t>
+  </si>
+  <si>
+    <t>0.0020,0.9948,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.5687,0.0274,0.6136,0.0052</t>
+  </si>
+  <si>
+    <t>0.3394,0.4498,0.2490,0.0019</t>
+  </si>
+  <si>
+    <t>0.0113,0.6900,0.4368,0.0012</t>
+  </si>
+  <si>
+    <t>0.0005,0.8680,0.9661,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.8243,0.9385,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.9875,0.0459,0.0005</t>
+  </si>
+  <si>
+    <t>0.0024,0.9266,0.7868,0.0013</t>
+  </si>
+  <si>
+    <t>0.0992,0.0018,0.0051,0.9503</t>
+  </si>
+  <si>
+    <t>0.0016,0.0382,0.0007,0.9964</t>
+  </si>
+  <si>
+    <t>0.0044,0.0110,0.0006,0.9966</t>
+  </si>
+  <si>
+    <t>0.0152,0.0020,0.0009,0.9939</t>
+  </si>
+  <si>
+    <t>0.0091,0.0021,0.0032,0.9941</t>
+  </si>
+  <si>
+    <t>0.0139,0.0020,0.0010,0.9945</t>
+  </si>
+  <si>
+    <t>0.0009,0.9705,0.5938,0.0018</t>
+  </si>
+  <si>
+    <t>0.0023,0.5165,0.9766,0.0004</t>
+  </si>
+  <si>
+    <t>0.0080,0.1169,0.9763,0.0002</t>
+  </si>
+  <si>
+    <t>0.0094,0.5234,0.9181,0.0015</t>
+  </si>
+  <si>
+    <t>0.0011,0.9154,0.9292,0.0003</t>
+  </si>
+  <si>
+    <t>0.0016,0.9608,0.4586,0.0002</t>
+  </si>
+  <si>
+    <t>0.9979,0.0012,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9881,0.0102,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.9809,0.0378,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9969,0.0015,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9957,0.0046,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9950,0.0029,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9933,0.0070,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9861,0.0166,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9969,0.0009,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0014,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9979,0.0011,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0012,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9974,0.0021,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0132,0.0022,0.9846,0.0062</t>
+  </si>
+  <si>
+    <t>0.0272,0.0051,0.9567,0.0260</t>
+  </si>
+  <si>
+    <t>0.8527,0.0111,0.1121,0.0095</t>
+  </si>
+  <si>
+    <t>0.0137,0.0025,0.9857,0.0009</t>
+  </si>
+  <si>
+    <t>0.1101,0.9194,0.0032,0.0007</t>
+  </si>
+  <si>
+    <t>0.0708,0.9401,0.0143,0.0005</t>
+  </si>
+  <si>
+    <t>0.0640,0.9311,0.0184,0.0004</t>
+  </si>
+  <si>
+    <t>0.3580,0.7844,0.0033,0.0007</t>
+  </si>
+  <si>
+    <t>0.0219,0.9766,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.0056,0.9901,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.6977,0.4502,0.0091,0.0031</t>
+  </si>
+  <si>
+    <t>0.8438,0.0558,0.0873,0.0036</t>
+  </si>
+  <si>
+    <t>0.5310,0.0063,0.7002,0.0004</t>
+  </si>
+  <si>
+    <t>0.4925,0.3728,0.0561,0.0380</t>
+  </si>
+  <si>
+    <t>0.6555,0.0541,0.3623,0.0118</t>
+  </si>
+  <si>
+    <t>0.2291,0.3609,0.0517,0.6919</t>
+  </si>
+  <si>
+    <t>0.0153,0.9720,0.0044,0.0020</t>
+  </si>
+  <si>
+    <t>0.0455,0.9270,0.0355,0.0044</t>
+  </si>
+  <si>
+    <t>0.0124,0.9570,0.0047,0.0278</t>
+  </si>
+  <si>
+    <t>0.0054,0.7381,0.8902,0.0019</t>
+  </si>
+  <si>
+    <t>0.0128,0.9854,0.0077,0.0002</t>
+  </si>
+  <si>
+    <t>0.9254,0.1438,0.0041,0.0003</t>
+  </si>
+  <si>
+    <t>0.7280,0.4191,0.0067,0.0007</t>
+  </si>
+  <si>
+    <t>0.9645,0.0196,0.0043,0.0053</t>
+  </si>
+  <si>
+    <t>0.9949,0.0005,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9860,0.0011,0.0001,0.0086</t>
+  </si>
+  <si>
+    <t>0.9911,0.0036,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9977,0.0003,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9824,0.0067,0.0038,0.0016</t>
+  </si>
+  <si>
+    <t>0.9963,0.0015,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9959,0.0010,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.0130,0.4539,0.9189,0.0054</t>
+  </si>
+  <si>
+    <t>0.0074,0.7386,0.5901,0.0002</t>
+  </si>
+  <si>
+    <t>0.0098,0.6024,0.8640,0.0008</t>
+  </si>
+  <si>
+    <t>0.0897,0.0401,0.9087,0.0010</t>
+  </si>
+  <si>
+    <t>0.7968,0.0833,0.0839,0.0124</t>
+  </si>
+  <si>
+    <t>0.6672,0.0651,0.3070,0.0505</t>
+  </si>
+  <si>
+    <t>0.2800,0.0262,0.7783,0.0152</t>
+  </si>
+  <si>
+    <t>0.5306,0.1189,0.4467,0.0162</t>
+  </si>
+  <si>
+    <t>0.0920,0.0012,0.0011,0.9661</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.0080,0.0034,0.0004,0.9962</t>
+  </si>
+  <si>
+    <t>0.0862,0.0007,0.0041,0.9595</t>
+  </si>
+  <si>
+    <t>0.0064,0.6491,0.8196,0.0103</t>
+  </si>
+  <si>
+    <t>0.9872,0.0080,0.0024,0.0006</t>
+  </si>
+  <si>
+    <t>0.5551,0.4856,0.0096,0.0155</t>
+  </si>
+  <si>
+    <t>0.7196,0.2213,0.0002,0.0046</t>
+  </si>
+  <si>
+    <t>0.6674,0.5618,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.9924,0.0008,0.0001,0.0026</t>
+  </si>
+  <si>
+    <t>0.4437,0.0039,0.0078,0.7077</t>
+  </si>
+  <si>
+    <t>0.9962,0.0020,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0029,0.0207,0.9775,0.0303</t>
+  </si>
+  <si>
+    <t>0.9870,0.0003,0.0009,0.0064</t>
+  </si>
+  <si>
+    <t>0.9067,0.0020,0.0018,0.1166</t>
+  </si>
+  <si>
+    <t>0.3524,0.5798,0.0071,0.0344</t>
+  </si>
+  <si>
+    <t>0.8620,0.1226,0.0197,0.0073</t>
+  </si>
+  <si>
+    <t>0.8985,0.0573,0.0431,0.0027</t>
+  </si>
+  <si>
+    <t>0.4321,0.5782,0.0230,0.0098</t>
+  </si>
+  <si>
+    <t>0.9094,0.0675,0.0260,0.0023</t>
+  </si>
+  <si>
+    <t>0.9092,0.0754,0.0094,0.0052</t>
+  </si>
+  <si>
+    <t>0.9943,0.0031,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9948,0.0010,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.9919,0.0080,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9961,0.0010,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9934,0.0009,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.9933,0.0040,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9973,0.0003,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9980,0.0002,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.6557,0.4898,0.0093,0.0046</t>
+  </si>
+  <si>
+    <t>0.7632,0.4329,0.0021,0.0008</t>
+  </si>
+  <si>
+    <t>0.6899,0.5055,0.0033,0.0002</t>
+  </si>
+  <si>
+    <t>0.5980,0.4956,0.0344,0.0025</t>
+  </si>
+  <si>
+    <t>0.9831,0.0243,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9760,0.0175,0.0060,0.0006</t>
+  </si>
+  <si>
+    <t>0.9865,0.0124,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.2544,0.7946,0.0095,0.0029</t>
+  </si>
+  <si>
+    <t>0.0028,0.0173,0.9937,0.0004</t>
+  </si>
+  <si>
+    <t>0.9428,0.0865,0.0054,0.0003</t>
+  </si>
+  <si>
+    <t>0.0073,0.0066,0.9842,0.0034</t>
+  </si>
+  <si>
+    <t>0.0268,0.1480,0.9360,0.0034</t>
+  </si>
+  <si>
+    <t>0.0972,0.0105,0.9318,0.0011</t>
+  </si>
+  <si>
+    <t>0.0261,0.0648,0.9342,0.0051</t>
+  </si>
+  <si>
+    <t>0.0050,0.0041,0.9920,0.0009</t>
+  </si>
+  <si>
+    <t>0.0145,0.0011,0.9859,0.0014</t>
+  </si>
+  <si>
+    <t>0.0410,0.0066,0.9573,0.0019</t>
+  </si>
+  <si>
+    <t>0.2140,0.2442,0.6555,0.0354</t>
+  </si>
+  <si>
+    <t>0.1579,0.0798,0.8255,0.0156</t>
+  </si>
+  <si>
+    <t>0.2834,0.2779,0.5113,0.0056</t>
+  </si>
+  <si>
+    <t>0.1644,0.6901,0.1444,0.0023</t>
+  </si>
+  <si>
+    <t>0.0226,0.9100,0.1629,0.0028</t>
+  </si>
+  <si>
+    <t>0.5690,0.3532,0.0855,0.0046</t>
+  </si>
+  <si>
+    <t>0.5973,0.1209,0.1830,0.1720</t>
+  </si>
+  <si>
+    <t>0.2746,0.1759,0.6853,0.0309</t>
+  </si>
+  <si>
+    <t>0.4047,0.7968,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.5490,0.7141,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.7722,0.3936,0.0026,0.0001</t>
+  </si>
+  <si>
+    <t>0.9930,0.0105,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.8676,0.3067,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.3449,0.0925,0.6626,0.0077</t>
+  </si>
+  <si>
+    <t>0.8127,0.0308,0.1670,0.0038</t>
+  </si>
+  <si>
+    <t>0.2192,0.6084,0.0897,0.2097</t>
+  </si>
+  <si>
+    <t>0.4476,0.0154,0.4820,0.0855</t>
+  </si>
+  <si>
+    <t>0.9447,0.0022,0.0261,0.0076</t>
+  </si>
+  <si>
+    <t>0.0217,0.0154,0.9531,0.0336</t>
+  </si>
+  <si>
+    <t>0.0903,0.4486,0.6696,0.0181</t>
+  </si>
+  <si>
+    <t>0.0940,0.0395,0.8099,0.0670</t>
+  </si>
+  <si>
+    <t>0.0786,0.0256,0.8808,0.0359</t>
+  </si>
+  <si>
+    <t>0.0086,0.8550,0.2962,0.0042</t>
+  </si>
+  <si>
+    <t>0.9981,0.0003,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9946,0.0044,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9951,0.0023,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9898,0.0080,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9847,0.0171,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9975,0.0004,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9979,0.0003,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.1138,0.0445,0.9100,0.0016</t>
+  </si>
+  <si>
+    <t>0.1094,0.6825,0.4579,0.0040</t>
+  </si>
+  <si>
+    <t>0.8510,0.0396,0.0828,0.0213</t>
+  </si>
+  <si>
+    <t>0.0213,0.0150,0.9680,0.0083</t>
+  </si>
+  <si>
+    <t>0.0026,0.0031,0.9954,0.0006</t>
+  </si>
+  <si>
+    <t>0.0166,0.6451,0.4194,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.0016,0.9982,0.0032</t>
+  </si>
+  <si>
+    <t>0.0349,0.0552,0.9404,0.0014</t>
+  </si>
+  <si>
+    <t>0.0069,0.0065,0.9891,0.0018</t>
+  </si>
+  <si>
+    <t>0.0152,0.0116,0.9431,0.0372</t>
+  </si>
+  <si>
+    <t>0.3013,0.1247,0.6524,0.0583</t>
+  </si>
+  <si>
+    <t>0.8319,0.0057,0.1250,0.0194</t>
+  </si>
+  <si>
+    <t>0.2128,0.0117,0.8494,0.0070</t>
+  </si>
+  <si>
+    <t>0.8842,0.0036,0.0894,0.0111</t>
+  </si>
+  <si>
+    <t>0.9875,0.0171,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9923,0.0071,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9955,0.0059,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9839,0.0280,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9951,0.0012,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9880,0.0214,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9915,0.0086,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9951,0.0029,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0717,0.2746,0.6717,0.0046</t>
+  </si>
+  <si>
+    <t>0.0089,0.0718,0.9699,0.0010</t>
+  </si>
+  <si>
+    <t>0.0082,0.1795,0.9513,0.0043</t>
+  </si>
+  <si>
+    <t>0.2275,0.0095,0.8629,0.0011</t>
+  </si>
+  <si>
+    <t>0.0278,0.0052,0.9757,0.0016</t>
+  </si>
+  <si>
+    <t>0.0278,0.0250,0.8192,0.3593</t>
+  </si>
+  <si>
+    <t>0.1171,0.0118,0.8394,0.0678</t>
+  </si>
+  <si>
+    <t>0.0751,0.0378,0.8883,0.0281</t>
+  </si>
+  <si>
+    <t>0.7249,0.0002,0.0007,0.4507</t>
+  </si>
+  <si>
+    <t>0.0065,0.1132,0.0023,0.9879</t>
+  </si>
+  <si>
+    <t>0.0308,0.0014,0.0009,0.9885</t>
+  </si>
+  <si>
+    <t>0.0028,0.0002,0.0001,0.9989</t>
+  </si>
+  <si>
+    <t>0.0020,0.0015,0.0003,0.9988</t>
+  </si>
+  <si>
+    <t>0.5855,0.0189,0.0160,0.4546</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,10 +2144,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,10 +2172,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2270,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2287,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2452,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,10 +2466,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2483,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,10 +2914,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2928,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,10 +2942,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,10 +2998,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3124,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3141,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3166,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3547,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,10 +3572,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3586,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3603,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3712,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3838,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3852,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,10 +3866,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,10 +4006,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4034,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4062,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4090,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4163,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4205,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4356,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4370,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4384,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4401,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,10 +4454,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4625,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4667,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4681,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4695,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4709,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4720,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4765,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4776,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,10 +4804,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4818,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4905,7 @@
         <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,7 +5045,7 @@
         <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,10 +5098,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5199,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5448,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
